--- a/Formula Excel Template.xlsx
+++ b/Formula Excel Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghanb\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghanb\OneDrive\Desktop\excel-analytics-functions-practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7956B136-4012-4C40-AC30-E71CA9344453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE75B7CB-0C4D-4DA6-AB1A-78F248B796B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="6" activeTab="6" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Max-Min" sheetId="9" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1092,6 +1092,10 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J10">CONCATENATE(B2:B10," ",C2:C10)</f>
+        <v>Jim Halpert</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
@@ -1121,6 +1125,9 @@
       <c r="I3" s="1">
         <v>42287</v>
       </c>
+      <c r="J3" t="str">
+        <v>Pam Beasley</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -1150,6 +1157,9 @@
       <c r="I4" s="1">
         <v>42986</v>
       </c>
+      <c r="J4" t="str">
+        <v>Dwight Schrute</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -1179,6 +1189,9 @@
       <c r="I5" s="1">
         <v>42341</v>
       </c>
+      <c r="J5" t="str">
+        <v>Angela Martin</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -1208,6 +1221,9 @@
       <c r="I6" s="1">
         <v>42977</v>
       </c>
+      <c r="J6" t="str">
+        <v>Toby Flenderson</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -1237,6 +1253,9 @@
       <c r="I7" s="1">
         <v>41528</v>
       </c>
+      <c r="J7" t="str">
+        <v>Michael Scott</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -1266,6 +1285,9 @@
       <c r="I8" s="1">
         <v>41551</v>
       </c>
+      <c r="J8" t="str">
+        <v>Meredith Palmer</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -1295,6 +1317,9 @@
       <c r="I9" s="1">
         <v>42116</v>
       </c>
+      <c r="J9" t="str">
+        <v>Stanley Hudson</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -1323,6 +1348,9 @@
       </c>
       <c r="I10" s="1">
         <v>40800</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Kevin Malone</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -2453,6 +2481,10 @@
         <f t="array" ref="K2:K10">LEFT(C2:C10,3)</f>
         <v>Hal</v>
       </c>
+      <c r="L2" t="str" cm="1">
+        <f t="array" ref="L2:L10">RIGHT(H2:H10,4)</f>
+        <v>2001</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
@@ -2488,6 +2520,9 @@
       <c r="K3" t="str">
         <v>Bea</v>
       </c>
+      <c r="L3" t="str">
+        <v>1999</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -2523,6 +2558,9 @@
       <c r="K4" t="str">
         <v>Sch</v>
       </c>
+      <c r="L4" t="str">
+        <v>2000</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -2558,6 +2596,9 @@
       <c r="K5" t="str">
         <v>Mar</v>
       </c>
+      <c r="L5" t="str">
+        <v>2000</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -2593,6 +2634,9 @@
       <c r="K6" t="str">
         <v>Fle</v>
       </c>
+      <c r="L6" t="str">
+        <v>2001</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -2628,6 +2672,9 @@
       <c r="K7" t="str">
         <v>Sco</v>
       </c>
+      <c r="L7" t="str">
+        <v>2001</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -2663,6 +2710,9 @@
       <c r="K8" t="str">
         <v>Pal</v>
       </c>
+      <c r="L8" t="str">
+        <v>2003</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -2698,6 +2748,9 @@
       <c r="K9" t="str">
         <v>Hud</v>
       </c>
+      <c r="L9" t="str">
+        <v>2002</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -2732,6 +2785,9 @@
       </c>
       <c r="K10" t="str">
         <v>Mal</v>
+      </c>
+      <c r="L10" t="str">
+        <v>2003</v>
       </c>
     </row>
   </sheetData>
@@ -2811,6 +2867,10 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J10">TEXT(H2:H10,"dd/mm/yyyy")</f>
+        <v>02/11/2001</v>
+      </c>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -2841,6 +2901,9 @@
       <c r="I3" s="1">
         <v>42287</v>
       </c>
+      <c r="J3" t="str">
+        <v>03/10/1999</v>
+      </c>
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -2871,6 +2934,9 @@
       <c r="I4" s="1">
         <v>42986</v>
       </c>
+      <c r="J4" t="str">
+        <v>04/07/2000</v>
+      </c>
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -2901,6 +2967,9 @@
       <c r="I5" s="1">
         <v>42341</v>
       </c>
+      <c r="J5" t="str">
+        <v>05/01/2000</v>
+      </c>
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -2931,6 +3000,9 @@
       <c r="I6" s="1">
         <v>42977</v>
       </c>
+      <c r="J6" t="str">
+        <v>06/05/2001</v>
+      </c>
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -2961,6 +3033,9 @@
       <c r="I7" s="1">
         <v>41528</v>
       </c>
+      <c r="J7" t="str">
+        <v>07/12/1995</v>
+      </c>
       <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -2991,6 +3066,9 @@
       <c r="I8" s="1">
         <v>41551</v>
       </c>
+      <c r="J8" t="str">
+        <v>08/11/2003</v>
+      </c>
       <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -3021,6 +3099,9 @@
       <c r="I9" s="1">
         <v>42116</v>
       </c>
+      <c r="J9" t="str">
+        <v>09/06/2002</v>
+      </c>
       <c r="K9" s="2"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -3050,6 +3131,9 @@
       </c>
       <c r="I10" s="1">
         <v>40800</v>
+      </c>
+      <c r="J10" t="str">
+        <v>10/08/2003</v>
       </c>
       <c r="K10" s="2"/>
     </row>
@@ -3139,6 +3223,10 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J10">TRIM(C2:C10)</f>
+        <v>Halpert</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3">
@@ -3168,6 +3256,9 @@
       <c r="I3" s="1">
         <v>42287</v>
       </c>
+      <c r="J3" t="str">
+        <v>Beasley</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -3197,6 +3288,9 @@
       <c r="I4" s="1">
         <v>42986</v>
       </c>
+      <c r="J4" t="str">
+        <v>Schrute</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -3226,6 +3320,9 @@
       <c r="I5" s="1">
         <v>42341</v>
       </c>
+      <c r="J5" t="str">
+        <v>Martin</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -3255,6 +3352,9 @@
       <c r="I6" s="1">
         <v>42977</v>
       </c>
+      <c r="J6" t="str">
+        <v>Flenderson</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -3284,6 +3384,9 @@
       <c r="I7" s="1">
         <v>41528</v>
       </c>
+      <c r="J7" t="str">
+        <v>Scott</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -3313,6 +3416,9 @@
       <c r="I8" s="1">
         <v>41551</v>
       </c>
+      <c r="J8" t="str">
+        <v>Palmer</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -3342,6 +3448,9 @@
       <c r="I9" s="1">
         <v>42116</v>
       </c>
+      <c r="J9" t="str">
+        <v>Hudson</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -3370,6 +3479,9 @@
       </c>
       <c r="I10" s="1">
         <v>40800</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Malone</v>
       </c>
     </row>
   </sheetData>
@@ -3455,6 +3567,10 @@
       <c r="I2" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="L2" t="str" cm="1">
+        <f t="array" ref="L2:L10">SUBSTITUTE(H2:H10, "/", "-")</f>
+        <v>11-2-2001</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
@@ -3484,6 +3600,9 @@
       <c r="I3" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="L3" t="str">
+        <v>10-3-1999</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -3513,6 +3632,9 @@
       <c r="I4" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="L4" t="str">
+        <v>7-4-2000</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -3542,6 +3664,9 @@
       <c r="I5" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="L5" t="str">
+        <v>1-5-2000</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -3571,6 +3696,9 @@
       <c r="I6" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="L6" t="str">
+        <v>5-6-2001</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -3600,6 +3728,9 @@
       <c r="I7" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="L7" t="str">
+        <v>5-6-2001</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -3629,6 +3760,9 @@
       <c r="I8" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="L8" t="str">
+        <v>11-8-2003</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -3658,6 +3792,9 @@
       <c r="I9" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="L9" t="str">
+        <v>6-9-2002</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -3686,6 +3823,9 @@
       </c>
       <c r="I10" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="L10" t="str">
+        <v>8-10-2003</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">

--- a/Formula Excel Template.xlsx
+++ b/Formula Excel Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghanb\OneDrive\Desktop\excel-analytics-functions-practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE75B7CB-0C4D-4DA6-AB1A-78F248B796B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4BB6C9-3C08-4849-8819-164F1C6A752E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="6" activeTab="6" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="6" activeTab="10" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Max-Min" sheetId="9" r:id="rId1"/>
@@ -1445,6 +1445,14 @@
       <c r="I2" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="J2">
+        <f>_xlfn.DAYS(I2,H2)</f>
+        <v>5056</v>
+      </c>
+      <c r="K2">
+        <f>NETWORKDAYS(H2,I2)</f>
+        <v>3611</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3">
@@ -1474,6 +1482,10 @@
       <c r="I3" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J10" si="0">_xlfn.DAYS(I3,H3)</f>
+        <v>5851</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -1503,6 +1515,10 @@
       <c r="I4" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>6275</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -1532,6 +1548,10 @@
       <c r="I5" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>5811</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -1561,6 +1581,10 @@
       <c r="I6" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>5960</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -1590,6 +1614,10 @@
       <c r="I7" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>4511</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -1619,6 +1647,10 @@
       <c r="I8" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>3595</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -1648,6 +1680,10 @@
       <c r="I9" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>4700</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -1676,6 +1712,10 @@
       </c>
       <c r="I10" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>4273</v>
       </c>
     </row>
   </sheetData>
@@ -3944,6 +3984,18 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
+      <c r="J2">
+        <f>SUM(G2:G10)</f>
+        <v>437000</v>
+      </c>
+      <c r="K2">
+        <f>SUMIF(G2:G10,"&gt;50000")</f>
+        <v>128000</v>
+      </c>
+      <c r="L2">
+        <f>SUMIFS(G2:G10,E2:E10,"female",D2:D10,"&lt;31")</f>
+        <v>36000</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
@@ -4260,6 +4312,18 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
+      <c r="J2">
+        <f>COUNT(G2:G10)</f>
+        <v>9</v>
+      </c>
+      <c r="K2">
+        <f>COUNTIF(G2:G10,"&gt;50000")</f>
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <f>COUNTIFS(D2:D10,"&gt;30",E2:E10,"male")</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
